--- a/Risaa_Homes_Product_Listing_Template.xlsx
+++ b/Risaa_Homes_Product_Listing_Template.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="❄️ Blankets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🧣 Flannel" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="☀️ Summer — Shagun Set" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="☀️ Summer — Comforter" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="☀️ Summer — Bed Sheets" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="☀️ Summer — Pillows" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="☀️ Summer — Mattress" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🌨️ Winter Comforter" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="📋 Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="❄️ Blankets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="🧣 Flannel" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="☀️ Summer — Shagun Set" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="☀️ Summer — Comforter" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="☀️ Summer — Bed Sheets" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="☀️ Summer — Pillows" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="☀️ Summer — Mattress" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="🌨️ Winter Comforter" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-BLK-RM-01</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
@@ -1181,7 +1181,11 @@
           <t>Mink</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr"/>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Double Bed</t>
+        </is>
+      </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
           <t>Mink</t>
@@ -1191,7 +1195,7 @@
       <c r="H4" s="21" t="inlineStr"/>
       <c r="I4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Heritage Rose</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr"/>
@@ -1200,12 +1204,14 @@
           <t>1 Blanket</t>
         </is>
       </c>
-      <c r="L4" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="M4" s="21" t="inlineStr"/>
+      <c r="L4" s="19" t="n">
+        <v>2299</v>
+      </c>
+      <c r="M4" s="21" t="inlineStr">
+        <is>
+          <t>2.2 kg</t>
+        </is>
+      </c>
       <c r="N4" s="20" t="inlineStr">
         <is>
           <t>Dry Clean</t>
@@ -1218,12 +1224,18 @@
       </c>
       <c r="P4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q4" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" s="21" t="n">
+        <v>3</v>
+      </c>
       <c r="R4" s="21" t="inlineStr"/>
-      <c r="S4" s="21" t="inlineStr"/>
+      <c r="S4" s="21" t="inlineStr">
+        <is>
+          <t>Soft mink blanket in romantic floral colourways. Dry clean.</t>
+        </is>
+      </c>
       <c r="T4" s="21" t="inlineStr"/>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -1234,7 +1246,7 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-BLK-RM-02</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -1247,7 +1259,11 @@
           <t>Mink</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr"/>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>Double Bed</t>
+        </is>
+      </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
           <t>Mink</t>
@@ -1257,7 +1273,7 @@
       <c r="H5" s="23" t="inlineStr"/>
       <c r="I5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="J5" s="23" t="inlineStr"/>
@@ -1266,12 +1282,14 @@
           <t>1 Blanket</t>
         </is>
       </c>
-      <c r="L5" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="M5" s="23" t="inlineStr"/>
+      <c r="L5" s="19" t="n">
+        <v>2299</v>
+      </c>
+      <c r="M5" s="23" t="inlineStr">
+        <is>
+          <t>2.2 kg</t>
+        </is>
+      </c>
       <c r="N5" s="22" t="inlineStr">
         <is>
           <t>Dry Clean</t>
@@ -1284,10 +1302,12 @@
       </c>
       <c r="P5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q5" s="23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" s="23" t="n">
+        <v>3</v>
+      </c>
       <c r="R5" s="23" t="inlineStr"/>
       <c r="S5" s="23" t="inlineStr"/>
       <c r="T5" s="23" t="inlineStr"/>
@@ -1300,7 +1320,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-BLK-RF-01</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -1313,7 +1333,11 @@
           <t>Mink</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>Double Bed</t>
+        </is>
+      </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
           <t>Mink</t>
@@ -1327,7 +1351,7 @@
       </c>
       <c r="I6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>N01 Chocolate &amp; Pink</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr"/>
@@ -1336,12 +1360,14 @@
           <t>1 Blanket</t>
         </is>
       </c>
-      <c r="L6" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="M6" s="21" t="inlineStr"/>
+      <c r="L6" s="19" t="n">
+        <v>2499</v>
+      </c>
+      <c r="M6" s="21" t="inlineStr">
+        <is>
+          <t>2.2 kg</t>
+        </is>
+      </c>
       <c r="N6" s="20" t="inlineStr">
         <is>
           <t>Dry Clean</t>
@@ -1354,12 +1380,22 @@
       </c>
       <c r="P6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q6" s="21" t="inlineStr"/>
-      <c r="R6" s="21" t="inlineStr"/>
-      <c r="S6" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q6" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S6" s="21" t="inlineStr">
+        <is>
+          <t>Double bed mink blanket with feather emboss — 8 colourways across 4 designs.</t>
+        </is>
+      </c>
       <c r="T6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -1370,7 +1406,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-BLK-RF-02</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -1383,7 +1419,11 @@
           <t>Mink</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr"/>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>Double Bed</t>
+        </is>
+      </c>
       <c r="F7" s="22" t="inlineStr">
         <is>
           <t>Mink</t>
@@ -1397,7 +1437,7 @@
       </c>
       <c r="I7" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>N02 Mauve &amp; Peach</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr"/>
@@ -1406,12 +1446,14 @@
           <t>1 Blanket</t>
         </is>
       </c>
-      <c r="L7" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="M7" s="23" t="inlineStr"/>
+      <c r="L7" s="19" t="n">
+        <v>2499</v>
+      </c>
+      <c r="M7" s="23" t="inlineStr">
+        <is>
+          <t>2.2 kg</t>
+        </is>
+      </c>
       <c r="N7" s="22" t="inlineStr">
         <is>
           <t>Dry Clean</t>
@@ -1424,10 +1466,12 @@
       </c>
       <c r="P7" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q7" s="23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q7" s="23" t="n">
+        <v>2</v>
+      </c>
       <c r="R7" s="23" t="inlineStr"/>
       <c r="S7" s="23" t="inlineStr"/>
       <c r="T7" s="23" t="inlineStr"/>
@@ -1440,7 +1484,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-BLK-RC-01</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -1453,7 +1497,11 @@
           <t>Mink</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>Double Bed</t>
+        </is>
+      </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
           <t>Mink</t>
@@ -1463,7 +1511,7 @@
       <c r="H8" s="21" t="inlineStr"/>
       <c r="I8" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Royal Indigo</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr"/>
@@ -1472,12 +1520,14 @@
           <t>1 Blanket</t>
         </is>
       </c>
-      <c r="L8" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="M8" s="21" t="inlineStr"/>
+      <c r="L8" s="19" t="n">
+        <v>2799</v>
+      </c>
+      <c r="M8" s="21" t="inlineStr">
+        <is>
+          <t>2.4 kg</t>
+        </is>
+      </c>
       <c r="N8" s="20" t="inlineStr">
         <is>
           <t>Dry Clean</t>
@@ -1490,12 +1540,18 @@
       </c>
       <c r="P8" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q8" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q8" s="21" t="n">
+        <v>3</v>
+      </c>
       <c r="R8" s="21" t="inlineStr"/>
-      <c r="S8" s="21" t="inlineStr"/>
+      <c r="S8" s="21" t="inlineStr">
+        <is>
+          <t>Premium mink blanket. Deep, rich colours. Dry clean.</t>
+        </is>
+      </c>
       <c r="T8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -1506,7 +1562,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-BLK-CR-01</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -1519,7 +1575,11 @@
           <t>Mink</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr"/>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>Double Bed</t>
+        </is>
+      </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
           <t>Mink</t>
@@ -1529,7 +1589,7 @@
       <c r="H9" s="23" t="inlineStr"/>
       <c r="I9" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J9" s="23" t="inlineStr"/>
@@ -1538,12 +1598,14 @@
           <t>1 Blanket</t>
         </is>
       </c>
-      <c r="L9" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="M9" s="23" t="inlineStr"/>
+      <c r="L9" s="19" t="n">
+        <v>3499</v>
+      </c>
+      <c r="M9" s="23" t="inlineStr">
+        <is>
+          <t>2.6 kg</t>
+        </is>
+      </c>
       <c r="N9" s="22" t="inlineStr">
         <is>
           <t>Dry Clean</t>
@@ -1556,12 +1618,22 @@
       </c>
       <c r="P9" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q9" s="23" t="inlineStr"/>
-      <c r="R9" s="23" t="inlineStr"/>
-      <c r="S9" s="23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q9" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" s="23" t="inlineStr">
+        <is>
+          <t>Bestseller</t>
+        </is>
+      </c>
+      <c r="S9" s="23" t="inlineStr">
+        <is>
+          <t>Heavyweight mink blanket. Bold patterns, gold-tone borders.</t>
+        </is>
+      </c>
       <c r="T9" s="23" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -2168,7 +2240,7 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-FLN-BB-01</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
@@ -2181,7 +2253,11 @@
           <t>Baby</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr"/>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Baby (100 × 140 cm)</t>
+        </is>
+      </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
           <t>Flannel</t>
@@ -2191,7 +2267,7 @@
       <c r="H4" s="21" t="inlineStr"/>
       <c r="I4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Pearl White</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr"/>
@@ -2200,10 +2276,8 @@
           <t>1 Blanket</t>
         </is>
       </c>
-      <c r="L4" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L4" s="19" t="n">
+        <v>999</v>
       </c>
       <c r="M4" s="21" t="inlineStr"/>
       <c r="N4" s="20" t="inlineStr">
@@ -2218,12 +2292,18 @@
       </c>
       <c r="P4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q4" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" s="21" t="n">
+        <v>3</v>
+      </c>
       <c r="R4" s="21" t="inlineStr"/>
-      <c r="S4" s="21" t="inlineStr"/>
+      <c r="S4" s="21" t="inlineStr">
+        <is>
+          <t>Soft flannel baby blanket. Machine washable. India.</t>
+        </is>
+      </c>
       <c r="T4" s="21" t="inlineStr"/>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -2234,7 +2314,7 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-FLN-BB-02</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -2247,7 +2327,11 @@
           <t>Baby</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr"/>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>Baby (100 × 140 cm)</t>
+        </is>
+      </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
           <t>Flannel</t>
@@ -2257,7 +2341,7 @@
       <c r="H5" s="23" t="inlineStr"/>
       <c r="I5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Sky Blue</t>
         </is>
       </c>
       <c r="J5" s="23" t="inlineStr"/>
@@ -2266,10 +2350,8 @@
           <t>1 Blanket</t>
         </is>
       </c>
-      <c r="L5" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L5" s="19" t="n">
+        <v>999</v>
       </c>
       <c r="M5" s="23" t="inlineStr"/>
       <c r="N5" s="22" t="inlineStr">
@@ -2284,10 +2366,12 @@
       </c>
       <c r="P5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q5" s="23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" s="23" t="n">
+        <v>3</v>
+      </c>
       <c r="R5" s="23" t="inlineStr"/>
       <c r="S5" s="23" t="inlineStr"/>
       <c r="T5" s="23" t="inlineStr"/>
@@ -2300,7 +2384,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-FLN-SB-01</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -2313,7 +2397,11 @@
           <t>Single Bed (S/B)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>Single Bed</t>
+        </is>
+      </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
           <t>Flannel</t>
@@ -2323,7 +2411,7 @@
       <c r="H6" s="21" t="inlineStr"/>
       <c r="I6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Slate Blue</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr"/>
@@ -2332,10 +2420,8 @@
           <t>1 Blanket</t>
         </is>
       </c>
-      <c r="L6" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L6" s="19" t="n">
+        <v>1599</v>
       </c>
       <c r="M6" s="21" t="inlineStr"/>
       <c r="N6" s="20" t="inlineStr">
@@ -2350,12 +2436,18 @@
       </c>
       <c r="P6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q6" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q6" s="21" t="n">
+        <v>3</v>
+      </c>
       <c r="R6" s="21" t="inlineStr"/>
-      <c r="S6" s="21" t="inlineStr"/>
+      <c r="S6" s="21" t="inlineStr">
+        <is>
+          <t>Single bed flannel blanket. Machine washable. India.</t>
+        </is>
+      </c>
       <c r="T6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -2366,7 +2458,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-FLN-SB-02</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -2379,7 +2471,11 @@
           <t>Single Bed (S/B)</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr"/>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>Single Bed</t>
+        </is>
+      </c>
       <c r="F7" s="22" t="inlineStr">
         <is>
           <t>Flannel</t>
@@ -2389,7 +2485,7 @@
       <c r="H7" s="23" t="inlineStr"/>
       <c r="I7" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Teal</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr"/>
@@ -2398,10 +2494,8 @@
           <t>1 Blanket</t>
         </is>
       </c>
-      <c r="L7" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L7" s="19" t="n">
+        <v>1599</v>
       </c>
       <c r="M7" s="23" t="inlineStr"/>
       <c r="N7" s="22" t="inlineStr">
@@ -2416,10 +2510,12 @@
       </c>
       <c r="P7" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q7" s="23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q7" s="23" t="n">
+        <v>3</v>
+      </c>
       <c r="R7" s="23" t="inlineStr"/>
       <c r="S7" s="23" t="inlineStr"/>
       <c r="T7" s="23" t="inlineStr"/>
@@ -2432,7 +2528,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-FLN-DB-01</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -2445,7 +2541,11 @@
           <t>Double Bed (D/B)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>Double Bed</t>
+        </is>
+      </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
           <t>Flannel</t>
@@ -2455,7 +2555,7 @@
       <c r="H8" s="21" t="inlineStr"/>
       <c r="I8" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Slate Blue</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr"/>
@@ -2464,10 +2564,8 @@
           <t>1 Blanket</t>
         </is>
       </c>
-      <c r="L8" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L8" s="19" t="n">
+        <v>2199</v>
       </c>
       <c r="M8" s="21" t="inlineStr"/>
       <c r="N8" s="20" t="inlineStr">
@@ -2482,12 +2580,18 @@
       </c>
       <c r="P8" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q8" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q8" s="21" t="n">
+        <v>3</v>
+      </c>
       <c r="R8" s="21" t="inlineStr"/>
-      <c r="S8" s="21" t="inlineStr"/>
+      <c r="S8" s="21" t="inlineStr">
+        <is>
+          <t>Double bed flannel blanket. Machine washable. India.</t>
+        </is>
+      </c>
       <c r="T8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -2498,7 +2602,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-FLN-DB-02</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -2511,7 +2615,11 @@
           <t>Double Bed (D/B)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr"/>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>Double Bed</t>
+        </is>
+      </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
           <t>Flannel</t>
@@ -2521,7 +2629,7 @@
       <c r="H9" s="23" t="inlineStr"/>
       <c r="I9" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Midnight</t>
         </is>
       </c>
       <c r="J9" s="23" t="inlineStr"/>
@@ -2530,10 +2638,8 @@
           <t>1 Blanket</t>
         </is>
       </c>
-      <c r="L9" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L9" s="19" t="n">
+        <v>2199</v>
       </c>
       <c r="M9" s="23" t="inlineStr"/>
       <c r="N9" s="22" t="inlineStr">
@@ -2548,10 +2654,12 @@
       </c>
       <c r="P9" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q9" s="23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q9" s="23" t="n">
+        <v>3</v>
+      </c>
       <c r="R9" s="23" t="inlineStr"/>
       <c r="S9" s="23" t="inlineStr"/>
       <c r="T9" s="23" t="inlineStr"/>
@@ -2564,7 +2672,7 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-FLN-S6-01</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -2577,7 +2685,11 @@
           <t>S/6</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr"/>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>S/6 (Sofa)</t>
+        </is>
+      </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
           <t>Flannel</t>
@@ -2587,7 +2699,7 @@
       <c r="H10" s="21" t="inlineStr"/>
       <c r="I10" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Ivory</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr"/>
@@ -2596,10 +2708,8 @@
           <t>1 Blanket</t>
         </is>
       </c>
-      <c r="L10" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L10" s="19" t="n">
+        <v>2999</v>
       </c>
       <c r="M10" s="21" t="inlineStr"/>
       <c r="N10" s="20" t="inlineStr">
@@ -2614,12 +2724,18 @@
       </c>
       <c r="P10" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q10" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q10" s="21" t="n">
+        <v>3</v>
+      </c>
       <c r="R10" s="21" t="inlineStr"/>
-      <c r="S10" s="21" t="inlineStr"/>
+      <c r="S10" s="21" t="inlineStr">
+        <is>
+          <t>Large 6-seater sofa flannel throw. Machine washable. India.</t>
+        </is>
+      </c>
       <c r="T10" s="21" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2630,7 +2746,7 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-FLN-S6-02</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -2643,7 +2759,11 @@
           <t>S/6</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr"/>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>S/6 (Sofa)</t>
+        </is>
+      </c>
       <c r="F11" s="22" t="inlineStr">
         <is>
           <t>Flannel</t>
@@ -2653,7 +2773,7 @@
       <c r="H11" s="23" t="inlineStr"/>
       <c r="I11" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Slate Blue</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr"/>
@@ -2662,10 +2782,8 @@
           <t>1 Blanket</t>
         </is>
       </c>
-      <c r="L11" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L11" s="19" t="n">
+        <v>2999</v>
       </c>
       <c r="M11" s="23" t="inlineStr"/>
       <c r="N11" s="22" t="inlineStr">
@@ -2680,10 +2798,12 @@
       </c>
       <c r="P11" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q11" s="23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q11" s="23" t="n">
+        <v>3</v>
+      </c>
       <c r="R11" s="23" t="inlineStr"/>
       <c r="S11" s="23" t="inlineStr"/>
       <c r="T11" s="23" t="inlineStr"/>
@@ -3292,7 +3412,7 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-SGN-01</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
@@ -3305,7 +3425,11 @@
           <t>Shagun Set</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr"/>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Double (90 × 100 in)</t>
+        </is>
+      </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
           <t>Cotton Blend</t>
@@ -3315,7 +3439,7 @@
       <c r="H4" s="21" t="inlineStr"/>
       <c r="I4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr"/>
@@ -3324,10 +3448,8 @@
           <t>1 Bedsheet + 2 Pillow Covers + 1 Comforter + ...</t>
         </is>
       </c>
-      <c r="L4" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L4" s="19" t="n">
+        <v>3499</v>
       </c>
       <c r="M4" s="21" t="inlineStr"/>
       <c r="N4" s="20" t="inlineStr">
@@ -3342,12 +3464,22 @@
       </c>
       <c r="P4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q4" s="21" t="inlineStr"/>
-      <c r="R4" s="21" t="inlineStr"/>
-      <c r="S4" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="R4" s="21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S4" s="21" t="inlineStr">
+        <is>
+          <t>5-piece printed double bed set — 1 bedsheet, 2 pillow covers, 2 cushion covers. 11 prints.</t>
+        </is>
+      </c>
       <c r="T4" s="20" t="inlineStr">
         <is>
           <t>Clarify exact 10-pc composition</t>
@@ -3362,7 +3494,7 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-SGN-02</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -3375,7 +3507,11 @@
           <t>Shagun Set</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr"/>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>Double (90 × 100 in)</t>
+        </is>
+      </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
           <t>Cotton Blend</t>
@@ -3385,7 +3521,7 @@
       <c r="H5" s="23" t="inlineStr"/>
       <c r="I5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Sky Blue</t>
         </is>
       </c>
       <c r="J5" s="23" t="inlineStr"/>
@@ -3394,10 +3530,8 @@
           <t>1 Bedsheet + 2 Pillow Covers + 1 Comforter + ...</t>
         </is>
       </c>
-      <c r="L5" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L5" s="19" t="n">
+        <v>3499</v>
       </c>
       <c r="M5" s="23" t="inlineStr"/>
       <c r="N5" s="22" t="inlineStr">
@@ -3412,10 +3546,12 @@
       </c>
       <c r="P5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q5" s="23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" s="23" t="n">
+        <v>11</v>
+      </c>
       <c r="R5" s="23" t="inlineStr"/>
       <c r="S5" s="23" t="inlineStr"/>
       <c r="T5" s="23" t="inlineStr"/>
@@ -3428,7 +3564,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-SGN-03</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -3441,7 +3577,11 @@
           <t>Shagun Set</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>Double (90 × 100 in)</t>
+        </is>
+      </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
           <t>Cotton Blend</t>
@@ -3451,7 +3591,7 @@
       <c r="H6" s="21" t="inlineStr"/>
       <c r="I6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Olive</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr"/>
@@ -3460,10 +3600,8 @@
           <t>1 Bedsheet + 2 Pillow Covers + 1 Comforter + ...</t>
         </is>
       </c>
-      <c r="L6" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L6" s="19" t="n">
+        <v>3499</v>
       </c>
       <c r="M6" s="21" t="inlineStr"/>
       <c r="N6" s="20" t="inlineStr">
@@ -3478,10 +3616,12 @@
       </c>
       <c r="P6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q6" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q6" s="21" t="n">
+        <v>11</v>
+      </c>
       <c r="R6" s="21" t="inlineStr"/>
       <c r="S6" s="21" t="inlineStr"/>
       <c r="T6" s="21" t="inlineStr"/>
@@ -4090,7 +4230,7 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-SCF-EMB-01</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
@@ -4103,7 +4243,11 @@
           <t>Comforter – Embroidery</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr"/>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
           <t>Cotton Shell, Poly-Fill</t>
@@ -4117,7 +4261,7 @@
       </c>
       <c r="I4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Ivory</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr"/>
@@ -4126,10 +4270,8 @@
           <t>1 Comforter</t>
         </is>
       </c>
-      <c r="L4" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L4" s="19" t="n">
+        <v>4499</v>
       </c>
       <c r="M4" s="21" t="inlineStr"/>
       <c r="N4" s="20" t="inlineStr">
@@ -4144,12 +4286,22 @@
       </c>
       <c r="P4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q4" s="21" t="inlineStr"/>
-      <c r="R4" s="21" t="inlineStr"/>
-      <c r="S4" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" s="21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S4" s="21" t="inlineStr">
+        <is>
+          <t>Embroidered cotton-shell summer comforter. Dry clean. India.</t>
+        </is>
+      </c>
       <c r="T4" s="21" t="inlineStr"/>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -4160,7 +4312,7 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-SCF-EMB-02</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -4173,7 +4325,11 @@
           <t>Comforter – Embroidery</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr"/>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
           <t>Cotton Shell, Poly-Fill</t>
@@ -4187,7 +4343,7 @@
       </c>
       <c r="I5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Champagne</t>
         </is>
       </c>
       <c r="J5" s="23" t="inlineStr"/>
@@ -4196,10 +4352,8 @@
           <t>1 Comforter</t>
         </is>
       </c>
-      <c r="L5" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L5" s="19" t="n">
+        <v>4499</v>
       </c>
       <c r="M5" s="23" t="inlineStr"/>
       <c r="N5" s="22" t="inlineStr">
@@ -4214,10 +4368,12 @@
       </c>
       <c r="P5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q5" s="23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" s="23" t="n">
+        <v>3</v>
+      </c>
       <c r="R5" s="23" t="inlineStr"/>
       <c r="S5" s="23" t="inlineStr"/>
       <c r="T5" s="23" t="inlineStr"/>
@@ -4230,7 +4386,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-SCF-PRT-01</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -4243,7 +4399,11 @@
           <t>Comforter – Printed</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
           <t>Cotton Shell, Poly-Fill</t>
@@ -4257,7 +4417,7 @@
       </c>
       <c r="I6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Teal</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr"/>
@@ -4266,10 +4426,8 @@
           <t>1 Comforter</t>
         </is>
       </c>
-      <c r="L6" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L6" s="19" t="n">
+        <v>3799</v>
       </c>
       <c r="M6" s="21" t="inlineStr"/>
       <c r="N6" s="20" t="inlineStr">
@@ -4284,12 +4442,22 @@
       </c>
       <c r="P6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q6" s="21" t="inlineStr"/>
-      <c r="R6" s="21" t="inlineStr"/>
-      <c r="S6" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q6" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S6" s="21" t="inlineStr">
+        <is>
+          <t>Printed cotton-shell summer comforter. Dry clean. India.</t>
+        </is>
+      </c>
       <c r="T6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -4300,7 +4468,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-SCF-PRT-02</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -4313,7 +4481,11 @@
           <t>Comforter – Printed</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr"/>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
       <c r="F7" s="22" t="inlineStr">
         <is>
           <t>Cotton Shell, Poly-Fill</t>
@@ -4327,7 +4499,7 @@
       </c>
       <c r="I7" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Slate Blue</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr"/>
@@ -4336,10 +4508,8 @@
           <t>1 Comforter</t>
         </is>
       </c>
-      <c r="L7" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L7" s="19" t="n">
+        <v>3799</v>
       </c>
       <c r="M7" s="23" t="inlineStr"/>
       <c r="N7" s="22" t="inlineStr">
@@ -4354,10 +4524,12 @@
       </c>
       <c r="P7" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q7" s="23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q7" s="23" t="n">
+        <v>2</v>
+      </c>
       <c r="R7" s="23" t="inlineStr"/>
       <c r="S7" s="23" t="inlineStr"/>
       <c r="T7" s="23" t="inlineStr"/>
@@ -4966,7 +5138,7 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-BS-12-01</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
@@ -4979,7 +5151,11 @@
           <t>1+2 (Bedsheet + 2 Pillow Covers)</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr"/>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
           <t>Pure Cotton</t>
@@ -4993,7 +5169,7 @@
       <c r="H4" s="21" t="inlineStr"/>
       <c r="I4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Ivory</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr"/>
@@ -5002,10 +5178,8 @@
           <t>1 Bedsheet + 2 Pillow Covers</t>
         </is>
       </c>
-      <c r="L4" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L4" s="19" t="n">
+        <v>1699</v>
       </c>
       <c r="M4" s="21" t="inlineStr"/>
       <c r="N4" s="20" t="inlineStr">
@@ -5020,12 +5194,18 @@
       </c>
       <c r="P4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q4" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" s="21" t="n">
+        <v>3</v>
+      </c>
       <c r="R4" s="21" t="inlineStr"/>
-      <c r="S4" s="21" t="inlineStr"/>
+      <c r="S4" s="21" t="inlineStr">
+        <is>
+          <t>180 TC pure cotton — 1 bedsheet + 2 pillow covers. Machine wash. India.</t>
+        </is>
+      </c>
       <c r="T4" s="21" t="inlineStr"/>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -5036,7 +5216,7 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-BS-12-02</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -5049,7 +5229,11 @@
           <t>1+2 (Bedsheet + 2 Pillow Covers)</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr"/>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
           <t>Pure Cotton</t>
@@ -5063,7 +5247,7 @@
       <c r="H5" s="23" t="inlineStr"/>
       <c r="I5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Sky Blue</t>
         </is>
       </c>
       <c r="J5" s="23" t="inlineStr"/>
@@ -5072,10 +5256,8 @@
           <t>1 Bedsheet + 2 Pillow Covers</t>
         </is>
       </c>
-      <c r="L5" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L5" s="19" t="n">
+        <v>1699</v>
       </c>
       <c r="M5" s="23" t="inlineStr"/>
       <c r="N5" s="22" t="inlineStr">
@@ -5090,10 +5272,12 @@
       </c>
       <c r="P5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q5" s="23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" s="23" t="n">
+        <v>3</v>
+      </c>
       <c r="R5" s="23" t="inlineStr"/>
       <c r="S5" s="23" t="inlineStr"/>
       <c r="T5" s="23" t="inlineStr"/>
@@ -5106,7 +5290,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-BS-121-01</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -5119,7 +5303,11 @@
           <t>1+2+1 (Bedsheet + 2 PC + 1 Slipcover)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
           <t>Pure Cotton</t>
@@ -5133,7 +5321,7 @@
       <c r="H6" s="21" t="inlineStr"/>
       <c r="I6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Ivory</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr"/>
@@ -5142,10 +5330,8 @@
           <t>1 Bedsheet + 2 Pillow Covers + 1 Slipcover</t>
         </is>
       </c>
-      <c r="L6" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L6" s="19" t="n">
+        <v>2299</v>
       </c>
       <c r="M6" s="21" t="inlineStr"/>
       <c r="N6" s="20" t="inlineStr">
@@ -5160,12 +5346,18 @@
       </c>
       <c r="P6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q6" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q6" s="21" t="n">
+        <v>3</v>
+      </c>
       <c r="R6" s="21" t="inlineStr"/>
-      <c r="S6" s="21" t="inlineStr"/>
+      <c r="S6" s="21" t="inlineStr">
+        <is>
+          <t>180 TC pure cotton — 1 bedsheet + 2 pillow covers + 1 slipcover.</t>
+        </is>
+      </c>
       <c r="T6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -5176,7 +5368,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-BS-121-02</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -5189,7 +5381,11 @@
           <t>1+2+1 (Bedsheet + 2 PC + 1 Slipcover)</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr"/>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
       <c r="F7" s="22" t="inlineStr">
         <is>
           <t>Pure Cotton</t>
@@ -5203,7 +5399,7 @@
       <c r="H7" s="23" t="inlineStr"/>
       <c r="I7" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Mustard</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr"/>
@@ -5212,10 +5408,8 @@
           <t>1 Bedsheet + 2 Pillow Covers + 1 Slipcover</t>
         </is>
       </c>
-      <c r="L7" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L7" s="19" t="n">
+        <v>2299</v>
       </c>
       <c r="M7" s="23" t="inlineStr"/>
       <c r="N7" s="22" t="inlineStr">
@@ -5230,10 +5424,12 @@
       </c>
       <c r="P7" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q7" s="23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q7" s="23" t="n">
+        <v>3</v>
+      </c>
       <c r="R7" s="23" t="inlineStr"/>
       <c r="S7" s="23" t="inlineStr"/>
       <c r="T7" s="23" t="inlineStr"/>
@@ -5246,7 +5442,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-BS-122-01</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -5259,7 +5455,11 @@
           <t>1+2+2 (Bedsheet + 2 PC + 2 Slipcovers)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
           <t>Pure Cotton</t>
@@ -5273,7 +5473,7 @@
       <c r="H8" s="21" t="inlineStr"/>
       <c r="I8" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Teal</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr"/>
@@ -5282,10 +5482,8 @@
           <t>1 Bedsheet + 2 Pillow Covers + 2 Slipcovers</t>
         </is>
       </c>
-      <c r="L8" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L8" s="19" t="n">
+        <v>2799</v>
       </c>
       <c r="M8" s="21" t="inlineStr"/>
       <c r="N8" s="20" t="inlineStr">
@@ -5300,12 +5498,18 @@
       </c>
       <c r="P8" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q8" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q8" s="21" t="n">
+        <v>3</v>
+      </c>
       <c r="R8" s="21" t="inlineStr"/>
-      <c r="S8" s="21" t="inlineStr"/>
+      <c r="S8" s="21" t="inlineStr">
+        <is>
+          <t>180 TC pure cotton — 1 bedsheet + 2 pillow covers + 2 slipcovers.</t>
+        </is>
+      </c>
       <c r="T8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -5316,7 +5520,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-BS-122-02</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -5329,7 +5533,11 @@
           <t>1+2+2 (Bedsheet + 2 PC + 2 Slipcovers)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr"/>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
           <t>Pure Cotton</t>
@@ -5343,7 +5551,7 @@
       <c r="H9" s="23" t="inlineStr"/>
       <c r="I9" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Burgundy</t>
         </is>
       </c>
       <c r="J9" s="23" t="inlineStr"/>
@@ -5352,10 +5560,8 @@
           <t>1 Bedsheet + 2 Pillow Covers + 2 Slipcovers</t>
         </is>
       </c>
-      <c r="L9" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L9" s="19" t="n">
+        <v>2799</v>
       </c>
       <c r="M9" s="23" t="inlineStr"/>
       <c r="N9" s="22" t="inlineStr">
@@ -5370,10 +5576,12 @@
       </c>
       <c r="P9" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q9" s="23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q9" s="23" t="n">
+        <v>3</v>
+      </c>
       <c r="R9" s="23" t="inlineStr"/>
       <c r="S9" s="23" t="inlineStr"/>
       <c r="T9" s="23" t="inlineStr"/>
@@ -5386,7 +5594,7 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-BS-123-01</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -5399,7 +5607,11 @@
           <t>1+2+3 (Bedsheet + 2 PC + 3 Slipcovers)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr"/>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
           <t>Pure Cotton</t>
@@ -5413,7 +5625,7 @@
       <c r="H10" s="21" t="inlineStr"/>
       <c r="I10" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Ivory</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr"/>
@@ -5422,10 +5634,8 @@
           <t>1 Bedsheet + 2 Pillow Covers + 3 Slipcovers</t>
         </is>
       </c>
-      <c r="L10" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L10" s="19" t="n">
+        <v>3499</v>
       </c>
       <c r="M10" s="21" t="inlineStr"/>
       <c r="N10" s="20" t="inlineStr">
@@ -5440,12 +5650,22 @@
       </c>
       <c r="P10" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q10" s="21" t="inlineStr"/>
-      <c r="R10" s="21" t="inlineStr"/>
-      <c r="S10" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q10" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" s="21" t="inlineStr">
+        <is>
+          <t>Bestseller</t>
+        </is>
+      </c>
+      <c r="S10" s="21" t="inlineStr">
+        <is>
+          <t>180 TC pure cotton — 1 bedsheet + 2 pillow covers + 3 slipcovers.</t>
+        </is>
+      </c>
       <c r="T10" s="21" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -5456,7 +5676,7 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-BS-123-02</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -5469,7 +5689,11 @@
           <t>1+2+3 (Bedsheet + 2 PC + 3 Slipcovers)</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr"/>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
       <c r="F11" s="22" t="inlineStr">
         <is>
           <t>Pure Cotton</t>
@@ -5483,7 +5707,7 @@
       <c r="H11" s="23" t="inlineStr"/>
       <c r="I11" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Royal Indigo</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr"/>
@@ -5492,10 +5716,8 @@
           <t>1 Bedsheet + 2 Pillow Covers + 3 Slipcovers</t>
         </is>
       </c>
-      <c r="L11" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L11" s="19" t="n">
+        <v>3499</v>
       </c>
       <c r="M11" s="23" t="inlineStr"/>
       <c r="N11" s="22" t="inlineStr">
@@ -5510,10 +5732,12 @@
       </c>
       <c r="P11" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q11" s="23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q11" s="23" t="n">
+        <v>3</v>
+      </c>
       <c r="R11" s="23" t="inlineStr"/>
       <c r="S11" s="23" t="inlineStr"/>
       <c r="T11" s="23" t="inlineStr"/>
@@ -6117,12 +6341,12 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t>Pillow – Variant 1</t>
+          <t>Pillow – Standard</t>
         </is>
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-PLW-STD-01</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
@@ -6135,13 +6359,21 @@
           <t>Pillow</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr"/>
-      <c r="F4" s="21" t="inlineStr"/>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Standard (43 × 69 cm)</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>Cotton Shell, Poly-Fill</t>
+        </is>
+      </c>
       <c r="G4" s="21" t="inlineStr"/>
       <c r="H4" s="21" t="inlineStr"/>
       <c r="I4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Pearl White</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr"/>
@@ -6150,10 +6382,8 @@
           <t>1 Pillow</t>
         </is>
       </c>
-      <c r="L4" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L4" s="19" t="n">
+        <v>499</v>
       </c>
       <c r="M4" s="21" t="inlineStr"/>
       <c r="N4" s="21" t="inlineStr"/>
@@ -6164,23 +6394,29 @@
       </c>
       <c r="P4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q4" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" s="21" t="n">
+        <v>3</v>
+      </c>
       <c r="R4" s="21" t="inlineStr"/>
-      <c r="S4" s="21" t="inlineStr"/>
+      <c r="S4" s="21" t="inlineStr">
+        <is>
+          <t>Standard sleeping pillow. India.</t>
+        </is>
+      </c>
       <c r="T4" s="21" t="inlineStr"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>Pillow – Variant 2</t>
+          <t>Pillow – Premium</t>
         </is>
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-PLW-PRM-01</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -6193,13 +6429,21 @@
           <t>Pillow</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr"/>
-      <c r="F5" s="23" t="inlineStr"/>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>Standard (43 × 69 cm)</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>Cotton Shell, High-Loft Poly-Fill</t>
+        </is>
+      </c>
       <c r="G5" s="23" t="inlineStr"/>
       <c r="H5" s="23" t="inlineStr"/>
       <c r="I5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Pearl White</t>
         </is>
       </c>
       <c r="J5" s="23" t="inlineStr"/>
@@ -6208,10 +6452,8 @@
           <t>1 Pillow</t>
         </is>
       </c>
-      <c r="L5" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L5" s="19" t="n">
+        <v>899</v>
       </c>
       <c r="M5" s="23" t="inlineStr"/>
       <c r="N5" s="23" t="inlineStr"/>
@@ -6222,23 +6464,33 @@
       </c>
       <c r="P5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q5" s="23" t="inlineStr"/>
-      <c r="R5" s="23" t="inlineStr"/>
-      <c r="S5" s="23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" s="23" t="inlineStr">
+        <is>
+          <t>Bestseller</t>
+        </is>
+      </c>
+      <c r="S5" s="23" t="inlineStr">
+        <is>
+          <t>Premium sleeping pillow, higher loft. India.</t>
+        </is>
+      </c>
       <c r="T5" s="23" t="inlineStr"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>Pillow – Variant 3</t>
+          <t>Pillow – Microfibre</t>
         </is>
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-PLW-MFB-01</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -6251,13 +6503,21 @@
           <t>Pillow</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>Standard (43 × 69 cm)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>Cotton Shell, Microfibre Fill</t>
+        </is>
+      </c>
       <c r="G6" s="21" t="inlineStr"/>
       <c r="H6" s="21" t="inlineStr"/>
       <c r="I6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Pearl White</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr"/>
@@ -6266,10 +6526,8 @@
           <t>1 Pillow</t>
         </is>
       </c>
-      <c r="L6" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L6" s="19" t="n">
+        <v>1199</v>
       </c>
       <c r="M6" s="21" t="inlineStr"/>
       <c r="N6" s="21" t="inlineStr"/>
@@ -6280,12 +6538,22 @@
       </c>
       <c r="P6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q6" s="21" t="inlineStr"/>
-      <c r="R6" s="21" t="inlineStr"/>
-      <c r="S6" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q6" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S6" s="21" t="inlineStr">
+        <is>
+          <t>Microfibre fill pillow. Hypoallergenic. India.</t>
+        </is>
+      </c>
       <c r="T6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -6887,12 +7155,12 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t>Mattress Cover – Variant 1</t>
+          <t>Mattress Cover – Standard</t>
         </is>
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-MTC-STD-01</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
@@ -6905,13 +7173,21 @@
           <t>Mattress Cover</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr"/>
-      <c r="F4" s="21" t="inlineStr"/>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Single / Double / Queen / King</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>Cotton-Polyester Blend</t>
+        </is>
+      </c>
       <c r="G4" s="21" t="inlineStr"/>
       <c r="H4" s="21" t="inlineStr"/>
       <c r="I4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Pearl White</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr"/>
@@ -6920,10 +7196,8 @@
           <t>1 Mattress Cover</t>
         </is>
       </c>
-      <c r="L4" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L4" s="19" t="n">
+        <v>1999</v>
       </c>
       <c r="M4" s="21" t="inlineStr"/>
       <c r="N4" s="20" t="inlineStr">
@@ -6938,23 +7212,29 @@
       </c>
       <c r="P4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q4" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" s="21" t="n">
+        <v>3</v>
+      </c>
       <c r="R4" s="21" t="inlineStr"/>
-      <c r="S4" s="21" t="inlineStr"/>
+      <c r="S4" s="21" t="inlineStr">
+        <is>
+          <t>Fitted mattress cover. Machine washable. India.</t>
+        </is>
+      </c>
       <c r="T4" s="21" t="inlineStr"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>Mattress Cover – Variant 2</t>
+          <t>Mattress Cover – Waterproof</t>
         </is>
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-MTC-WP-01</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -6967,13 +7247,21 @@
           <t>Mattress Cover</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr"/>
-      <c r="F5" s="23" t="inlineStr"/>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>Single / Double / Queen / King</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>Cotton Top, Waterproof Backing</t>
+        </is>
+      </c>
       <c r="G5" s="23" t="inlineStr"/>
       <c r="H5" s="23" t="inlineStr"/>
       <c r="I5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Pearl White</t>
         </is>
       </c>
       <c r="J5" s="23" t="inlineStr"/>
@@ -6982,10 +7270,8 @@
           <t>1 Mattress Cover</t>
         </is>
       </c>
-      <c r="L5" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L5" s="19" t="n">
+        <v>2699</v>
       </c>
       <c r="M5" s="23" t="inlineStr"/>
       <c r="N5" s="22" t="inlineStr">
@@ -7000,12 +7286,22 @@
       </c>
       <c r="P5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q5" s="23" t="inlineStr"/>
-      <c r="R5" s="23" t="inlineStr"/>
-      <c r="S5" s="23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" s="23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S5" s="23" t="inlineStr">
+        <is>
+          <t>Waterproof fitted mattress cover. Machine washable. India.</t>
+        </is>
+      </c>
       <c r="T5" s="23" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -7607,12 +7903,12 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t>Heavy Winter Comforter – Product 1</t>
+          <t>Heavy Winter Comforter – Solid</t>
         </is>
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-WCF-SOL-01</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
@@ -7625,17 +7921,25 @@
           <t>Heavy Winter</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr"/>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Single / Double</t>
+        </is>
+      </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
           <t>Cotton Shell, Heavy Poly-Fill</t>
         </is>
       </c>
       <c r="G4" s="21" t="inlineStr"/>
-      <c r="H4" s="21" t="inlineStr"/>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
       <c r="I4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Ivory</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr"/>
@@ -7644,10 +7948,8 @@
           <t>1 Comforter</t>
         </is>
       </c>
-      <c r="L4" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L4" s="19" t="n">
+        <v>4999</v>
       </c>
       <c r="M4" s="21" t="inlineStr"/>
       <c r="N4" s="20" t="inlineStr">
@@ -7662,23 +7964,33 @@
       </c>
       <c r="P4" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q4" s="21" t="inlineStr"/>
-      <c r="R4" s="21" t="inlineStr"/>
-      <c r="S4" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" s="21" t="inlineStr">
+        <is>
+          <t>Bestseller</t>
+        </is>
+      </c>
+      <c r="S4" s="21" t="inlineStr">
+        <is>
+          <t>Heavy poly-fill winter comforter. Solid colours. Dry clean.</t>
+        </is>
+      </c>
       <c r="T4" s="21" t="inlineStr"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>Heavy Winter Comforter – Product 2</t>
+          <t>Heavy Winter Comforter – Printed</t>
         </is>
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-WCF-PRT-01</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -7691,17 +8003,25 @@
           <t>Heavy Winter</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr"/>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>Single / Double</t>
+        </is>
+      </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
           <t>Cotton Shell, Heavy Poly-Fill</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr"/>
-      <c r="H5" s="23" t="inlineStr"/>
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t>Printed</t>
+        </is>
+      </c>
       <c r="I5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Teal</t>
         </is>
       </c>
       <c r="J5" s="23" t="inlineStr"/>
@@ -7710,10 +8030,8 @@
           <t>1 Comforter</t>
         </is>
       </c>
-      <c r="L5" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L5" s="19" t="n">
+        <v>5499</v>
       </c>
       <c r="M5" s="23" t="inlineStr"/>
       <c r="N5" s="22" t="inlineStr">
@@ -7728,23 +8046,33 @@
       </c>
       <c r="P5" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q5" s="23" t="inlineStr"/>
-      <c r="R5" s="23" t="inlineStr"/>
-      <c r="S5" s="23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" s="23" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="S5" s="23" t="inlineStr">
+        <is>
+          <t>Heavy poly-fill winter comforter. Printed shell. Dry clean.</t>
+        </is>
+      </c>
       <c r="T5" s="23" t="inlineStr"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>Heavy Winter Comforter – Product 3</t>
+          <t>Heavy Winter Comforter – Embroidery</t>
         </is>
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>RH-WCF-EMB-01</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -7757,17 +8085,25 @@
           <t>Heavy Winter</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>Double / Queen</t>
+        </is>
+      </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
           <t>Cotton Shell, Heavy Poly-Fill</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>Embroidery</t>
+        </is>
+      </c>
       <c r="I6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
+          <t>Champagne</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr"/>
@@ -7776,10 +8112,8 @@
           <t>1 Comforter</t>
         </is>
       </c>
-      <c r="L6" s="19" t="inlineStr">
-        <is>
-          <t>— fill in —</t>
-        </is>
+      <c r="L6" s="19" t="n">
+        <v>6999</v>
       </c>
       <c r="M6" s="21" t="inlineStr"/>
       <c r="N6" s="20" t="inlineStr">
@@ -7794,12 +8128,22 @@
       </c>
       <c r="P6" s="19" t="inlineStr">
         <is>
-          <t>— fill in —</t>
-        </is>
-      </c>
-      <c r="Q6" s="21" t="inlineStr"/>
-      <c r="R6" s="21" t="inlineStr"/>
-      <c r="S6" s="21" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q6" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t>Heirloom</t>
+        </is>
+      </c>
+      <c r="S6" s="21" t="inlineStr">
+        <is>
+          <t>Heavy poly-fill winter comforter. Embroidered shell. Dry clean.</t>
+        </is>
+      </c>
       <c r="T6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
